--- a/business_forms/047_customer_loyalty_data_access_request_form--business_forms.xlsx
+++ b/business_forms/047_customer_loyalty_data_access_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'customer_loyalty_data',_'label':_'customer_loyalty_data'}</t>
+          <t>customer_loyalty_data</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Customer Loyalty Data', 'label': 'Customer Loyalty Data'}</t>
+          <t>Customer Loyalty Data</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'customer_contact_information',_'label':_'customer_contact_information'}</t>
+          <t>customer_contact_information</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Customer Contact Information', 'label': 'Customer Contact Information'}</t>
+          <t>Customer Contact Information</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'customer_purchase_history',_'label':_'customer_purchase_history'}</t>
+          <t>customer_purchase_history</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Customer Purchase History', 'label': 'Customer Purchase History'}</t>
+          <t>Customer Purchase History</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'customer_loyalty_program_data',_'label':_'customer_loyalty_program_data'}</t>
+          <t>customer_loyalty_program_data</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Customer Loyalty Program Data', 'label': 'Customer Loyalty Program Data'}</t>
+          <t>Customer Loyalty Program Data</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'customer_marketing_data',_'label':_'customer_marketing_data'}</t>
+          <t>customer_marketing_data</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Customer Marketing Data', 'label': 'Customer Marketing Data'}</t>
+          <t>Customer Marketing Data</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'customer_financial_data',_'label':_'customer_financial_data'}</t>
+          <t>customer_financial_data</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Customer Financial Data', 'label': 'Customer Financial Data'}</t>
+          <t>Customer Financial Data</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'customer_support_data',_'label':_'customer_support_data'}</t>
+          <t>customer_support_data</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Customer Support Data', 'label': 'Customer Support Data'}</t>
+          <t>Customer Support Data</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'customer_other_data',_'label':_'customer_other_data'}</t>
+          <t>customer_other_data</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Customer Other Data', 'label': 'Customer Other Data'}</t>
+          <t>Customer Other Data</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'one_time',_'label':_'one_time'}</t>
+          <t>one_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'One time', 'label': 'One time'}</t>
+          <t>One time</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'recurring',_'label':_'recurring'}</t>
+          <t>recurring</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Recurring', 'label': 'Recurring'}</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'admin',_'label':_'admin'}</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Admin', 'label': 'Admin'}</t>
+          <t>Admin</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'supervisor',_'label':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Supervisor', 'label': 'Supervisor'}</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'support',_'label':_'support'}</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Support', 'label': 'Support'}</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
